--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="412">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -638,6 +638,11 @@
     <t>FR Core Organization Short Name Extension</t>
   </si>
   <si>
+    <t>Libellé court de l'organisation
++The Organization short name</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -653,6 +658,10 @@
   </si>
   <si>
     <t>FR Core Organization Description Extension</t>
+  </si>
+  <si>
+    <t>Description textuelle d'une organisation
+Organization description</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -3738,7 +3747,7 @@
         <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3798,7 +3807,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -3818,13 +3827,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -3846,13 +3855,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3912,7 +3921,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -3932,13 +3941,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -3960,13 +3969,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4046,10 +4055,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4075,16 +4084,16 @@
         <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4133,7 +4142,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4162,10 +4171,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4188,17 +4197,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4247,7 +4256,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4256,30 +4265,30 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4388,10 +4397,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4502,10 +4511,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4531,16 +4540,16 @@
         <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4565,11 +4574,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4587,7 +4596,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4605,7 +4614,7 @@
         <v>191</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4616,10 +4625,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4642,19 +4651,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4683,7 +4692,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4701,7 +4710,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4716,10 +4725,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -4730,10 +4739,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4759,16 +4768,16 @@
         <v>130</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4781,7 +4790,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -4817,7 +4826,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4832,13 +4841,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4846,10 +4855,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4875,13 +4884,13 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4895,7 +4904,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -4931,7 +4940,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4946,13 +4955,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4960,10 +4969,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4986,13 +4995,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5043,7 +5052,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5058,13 +5067,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5072,10 +5081,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5098,16 +5107,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5157,7 +5166,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5172,13 +5181,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5186,10 +5195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5212,70 +5221,70 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="R32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="R32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5290,24 +5299,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5330,19 +5339,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5371,7 +5380,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5389,7 +5398,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5404,24 +5413,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5447,16 +5456,16 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5505,7 +5514,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5514,19 +5523,19 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5534,10 +5543,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5563,16 +5572,16 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5621,7 +5630,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5639,7 +5648,7 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5650,10 +5659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5676,19 +5685,19 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5737,7 +5746,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5746,19 +5755,19 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5766,10 +5775,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5792,19 +5801,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5853,7 +5862,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5862,19 +5871,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5882,10 +5891,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5908,17 +5917,17 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5967,7 +5976,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5982,10 +5991,10 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>106</v>
@@ -5996,10 +6005,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6108,10 +6117,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6222,10 +6231,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6251,13 +6260,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6307,7 +6316,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6316,7 +6325,7 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
@@ -6336,10 +6345,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6365,13 +6374,13 @@
         <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6401,7 +6410,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6419,7 +6428,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6448,10 +6457,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6474,16 +6483,16 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6533,7 +6542,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6551,7 +6560,7 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6562,10 +6571,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6591,13 +6600,13 @@
         <v>102</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6647,7 +6656,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6676,10 +6685,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6702,19 +6711,19 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6763,7 +6772,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6781,7 +6790,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6792,10 +6801,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6904,10 +6913,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7018,14 +7027,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7047,16 +7056,16 @@
         <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7105,7 +7114,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7134,10 +7143,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7160,17 +7169,17 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7198,10 +7207,10 @@
         <v>150</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7219,7 +7228,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7237,7 +7246,7 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7248,10 +7257,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7274,17 +7283,17 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7333,7 +7342,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7348,10 +7357,10 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7362,10 +7371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7388,17 +7397,17 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7447,7 +7456,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7462,10 +7471,10 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7476,10 +7485,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7502,17 +7511,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7561,7 +7570,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7576,10 +7585,10 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -7590,10 +7599,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7616,17 +7625,17 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7675,7 +7684,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
